--- a/Mantenimiento/excels/ICA-ICA-ICA.xlsx
+++ b/Mantenimiento/excels/ICA-ICA-ICA.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -484,11 +484,6 @@
           <t>siniestros</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>mantenimiento</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -536,11 +531,6 @@
       <c r="K2" t="n">
         <v>0</v>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -588,11 +578,6 @@
       <c r="K3" t="n">
         <v>1</v>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -640,11 +625,6 @@
       <c r="K4" t="n">
         <v>0</v>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -692,11 +672,6 @@
       <c r="K5" t="n">
         <v>0</v>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -744,11 +719,6 @@
       <c r="K6" t="n">
         <v>0</v>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -796,11 +766,6 @@
       <c r="K7" t="n">
         <v>0</v>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -848,11 +813,6 @@
       <c r="K8" t="n">
         <v>0</v>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -900,11 +860,6 @@
       <c r="K9" t="n">
         <v>0</v>
       </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -952,11 +907,6 @@
       <c r="K10" t="n">
         <v>0</v>
       </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1003,11 +953,6 @@
       </c>
       <c r="K11" t="n">
         <v>0</v>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
       </c>
     </row>
   </sheetData>
